--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -12750,9 +12750,13 @@
         </is>
       </c>
       <c r="D637" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E637" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E637" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:22:05 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -12670,9 +12670,13 @@
         </is>
       </c>
       <c r="D633" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E633" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E633" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 12:42:36 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -13382,9 +13382,13 @@
         </is>
       </c>
       <c r="D669" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E669" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E669" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 12:17:22 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -10312,9 +10312,13 @@
         </is>
       </c>
       <c r="D511" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E511" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 12:52:25 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -8574,9 +8574,13 @@
         </is>
       </c>
       <c r="D421" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E421" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:51:13 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -12484,9 +12484,13 @@
         </is>
       </c>
       <c r="D623" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E623" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E623" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:06:00 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -2915,9 +2915,13 @@
         </is>
       </c>
       <c r="D128" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E128" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:22:14 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -15375,9 +15375,13 @@
         </is>
       </c>
       <c r="D772" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E772" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E772" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:12:18 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -10423,9 +10423,13 @@
         </is>
       </c>
       <c r="D516" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E516" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:15:58 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -26562,9 +26562,13 @@
         </is>
       </c>
       <c r="D1349" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1349" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1349" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 12:40:54 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1350">
       <c r="A1350" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -9814,9 +9814,13 @@
         </is>
       </c>
       <c r="D485" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E485" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 13:32:39 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -22952,9 +22952,13 @@
         </is>
       </c>
       <c r="D1163" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1163" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1163" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 16:27:44 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1164">
       <c r="A1164" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -24523,9 +24523,13 @@
         </is>
       </c>
       <c r="D1244" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1244" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1244" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:37:37 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1245">
       <c r="A1245" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20639,9 +20639,13 @@
         </is>
       </c>
       <c r="D1044" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1044" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1044" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:06:31 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1045">
       <c r="A1045" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -15079,9 +15079,13 @@
         </is>
       </c>
       <c r="D756" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E756" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E756" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02 14:27:43 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -5775,9 +5775,13 @@
         </is>
       </c>
       <c r="D276" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E276" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03 13:02:51 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -22812,9 +22812,13 @@
         </is>
       </c>
       <c r="D1155" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1155" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04 13:41:38 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1156">
       <c r="A1156" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -6886,9 +6886,13 @@
         </is>
       </c>
       <c r="D333" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E333" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:48:09 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -7563,9 +7563,13 @@
         </is>
       </c>
       <c r="D368" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E368" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:45:24 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -1006,9 +1006,13 @@
         </is>
       </c>
       <c r="D29" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:05:24 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -6833,9 +6833,13 @@
         </is>
       </c>
       <c r="D330" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E330" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:13:33 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -9758,9 +9758,13 @@
         </is>
       </c>
       <c r="D481" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E481" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:59:03 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -18309,9 +18309,13 @@
         </is>
       </c>
       <c r="D922" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E922" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E922" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10 14:14:00 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="923">
       <c r="A923" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -930,9 +930,13 @@
         </is>
       </c>
       <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:38:27 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20557,9 +20557,13 @@
         </is>
       </c>
       <c r="D1038" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1038" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1038" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 17:22:20 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1039">
       <c r="A1039" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -12391,9 +12391,13 @@
         </is>
       </c>
       <c r="D616" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E616" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E616" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:34:36 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -5049,9 +5049,13 @@
         </is>
       </c>
       <c r="D238" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E238" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:19:29 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -16819,9 +16819,13 @@
         </is>
       </c>
       <c r="D844" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E844" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E844" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:05:45 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="845">
       <c r="A845" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -24564,9 +24564,13 @@
         </is>
       </c>
       <c r="D1243" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1243" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1243" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:01:35 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1244">
       <c r="A1244" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -25166,9 +25166,13 @@
         </is>
       </c>
       <c r="D1273" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1273" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1273" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:59:04 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1274">
       <c r="A1274" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20946,9 +20946,13 @@
         </is>
       </c>
       <c r="D1057" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1057" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1057" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18 12:27:39 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1058">
       <c r="A1058" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -19865,9 +19865,13 @@
         </is>
       </c>
       <c r="D1002" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1002" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1002" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 15:17:20 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1003">
       <c r="A1003" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -16606,9 +16606,13 @@
         </is>
       </c>
       <c r="D833" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E833" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E833" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:20:41 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="834">
       <c r="A834" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -26114,9 +26114,13 @@
         </is>
       </c>
       <c r="D1321" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1321" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1321" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:26:19 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1322">
       <c r="A1322" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -1071,9 +1071,13 @@
         </is>
       </c>
       <c r="D32" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:27:33 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -2349,9 +2349,13 @@
         </is>
       </c>
       <c r="D98" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:05:15 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -7975,9 +7975,13 @@
         </is>
       </c>
       <c r="D388" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E388" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:27:44 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -12023,9 +12023,13 @@
         </is>
       </c>
       <c r="D596" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E596" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E596" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 12:58:12 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -15112,9 +15112,13 @@
         </is>
       </c>
       <c r="D755" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E755" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E755" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:51:28 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -5856,9 +5856,13 @@
         </is>
       </c>
       <c r="D279" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E279" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:58:03 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -18235,9 +18235,13 @@
         </is>
       </c>
       <c r="D916" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E916" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E916" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:52:24 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="917">
       <c r="A917" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -20887,9 +20887,13 @@
         </is>
       </c>
       <c r="D1052" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1052" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E1052" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:57:45 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="1053">
       <c r="A1053" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -9379,9 +9379,13 @@
         </is>
       </c>
       <c r="D460" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E460" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:51:10 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">

--- a/data/temas.xlsx
+++ b/data/temas.xlsx
@@ -7032,9 +7032,13 @@
         </is>
       </c>
       <c r="D339" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E339" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 14:17:52 UTC</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
